--- a/output/G50Max_抖音种草策略_上市势能版.xlsx
+++ b/output/G50Max_抖音种草策略_上市势能版.xlsx
@@ -535,8 +535,8 @@
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>认知蓄水
-痛点预埋 · 素材赛马 · 攒授权</t>
+          <t>新品蓄水
+G50 Max首晒预埋 · 痛点唤醒 · 素材赛马</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -596,7 +596,7 @@
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>5w（总盘闭环：1.3w＋2.2w＋1.5w）</t>
+          <t>6w（达人内容5w＋投流1w｜总盘闭环：1.4w＋3.0w＋1.6w）</t>
         </is>
       </c>
       <c r="D6" s="2" t="n"/>
@@ -611,21 +611,21 @@
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>26%（1.3w）</t>
+          <t>23%（1.4w）</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>44%（2.2w）</t>
+          <t>50%（3.0w）</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>30%（1.5w）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="78" customHeight="1">
+          <t>27%（1.6w）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="92" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>内容推广</t>
@@ -639,22 +639,24 @@
       <c r="C8" s="5" t="inlineStr">
         <is>
           <t>koc达人×2（2500/个）
+素人达人×8（800-1000/个）
+G50 Max置换达人×10
+（置换门槛：签星图授权＋二创授权≥30天，未授权不置换）</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>腰部达人×1（10000/个）
+koc达人×4（2500/个）
 素人达人×6（800-1000/个）
 G50 Max置换达人×10
-（置换门槛：签星图授权＋二创授权≥30天，未授权不置换）</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>腰部达人×1（10000/个）
-koc达人×2（2500/个）
-G50 Max置换达人×10
 （引爆周48小时内集中发布，统一挂话题）</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>素人达人×6（800-1000/个）
+          <t>koc达人×2（2500/个）
+素人达人×9-10（800-1000/个）
 G50 Max置换达人×10
 （按素材数据滚动补发）</t>
         </is>
@@ -669,17 +671,17 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>18条（其中授权素材≥10条）</t>
+          <t>20条（其中授权素材≥10条）</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>13条＋话题事件</t>
+          <t>21条＋话题事件</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>16条（合计≥47条，授权素材≥30条）</t>
+          <t>21-22条（合计≥62条，授权素材≥30条）</t>
         </is>
       </c>
     </row>
@@ -692,17 +694,17 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>1.0w</t>
+          <t>1.2w</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>1.5w</t>
+          <t>2.5w</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>0.5w</t>
+          <t>1.3w</t>
         </is>
       </c>
     </row>
@@ -748,17 +750,17 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
+          <t>0.2w</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>0.5w</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
           <t>0.3w</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>0.7w</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>1.0w</t>
         </is>
       </c>
     </row>
@@ -772,7 +774,7 @@
       <c r="C13" s="5" t="inlineStr">
         <is>
           <t>预埋型内容
-（痛点唤醒＋效果对比）</t>
+（G50 Max新品首晒＋痛点唤醒＋效果对比）</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -788,7 +790,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="110" customHeight="1">
+    <row r="14" ht="130" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>内容方向</t>
@@ -797,9 +799,10 @@
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>1. 落地分屏实测：同一镜头分屏「落地直连 vs 排队买卡/漫游」，结尾报网速（钩子：“落地关口，看谁先有网”）
-2. 天价漫游账单剧情：“出国7天，话费8000”→按当地套餐计费反转
-3. 家庭出游场景：海边度假/主题乐园/户外露营，记录亲子时刻，预埋16台设备共享</t>
+          <t>1. G50 Max新品首晒/开箱预告：“在CES被老外围观的中国设备，终于要在国内上了”——悬念式开箱，露产品露logo，预告天猫首发
+2. 落地分屏实测（G50 Max出镜）：同一镜头分屏「G50 Max落地直连 vs 排队买卡/漫游」，结尾报网速（钩子：“落地关口，看谁先有网”）
+3. 天价漫游账单剧情：“出国7天，话费8000”→掏出G50 Max，按当地套餐计费反转
+4. 家庭出游场景：海边/乐园/露营亲子时刻，G50 Max带16台设备共享预埋</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -857,7 +860,7 @@
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>总曝光≥800万｜有效素材≥47条（可投流授权素材≥30条）｜爆文率≥10%｜引爆周“G50 Max”搜索指数环比+300%｜A3种草人群资产≥15万｜引爆周天猫店访客环比+100%</t>
+          <t>总曝光≥1000万｜有效素材≥62条（可投流授权素材≥30条）｜爆文率≥10%｜引爆周“G50 Max”搜索指数环比+300%｜A3种草人群资产≥18万｜引爆周天猫店访客环比+100%</t>
         </is>
       </c>
       <c r="D17" s="2" t="n"/>
